--- a/data/trans_dic/IP17-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP17-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas</t>
+          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,56; 29,48</t>
+          <t>15,74; 30,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,66; 28,5</t>
+          <t>14,69; 28,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,69; 43,46</t>
+          <t>23,02; 42,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,01; 21,68</t>
+          <t>5,63; 20,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,79; 31,51</t>
+          <t>17,06; 31,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,02; 28,38</t>
+          <t>13,7; 28,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,38; 27,71</t>
+          <t>10,87; 26,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,81; 24,73</t>
+          <t>8,91; 25,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,99; 28,51</t>
+          <t>18,17; 28,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,9; 26,01</t>
+          <t>15,72; 25,82</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,43; 30,98</t>
+          <t>18,59; 30,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,24; 20,62</t>
+          <t>8,89; 20,04</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,92; 22,08</t>
+          <t>16,24; 22,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>19,21; 25,54</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17,02; 22,98</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11,43; 17,79</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>19,21; 25,49</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>16,89; 22,49</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>11,06; 17,58</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>19,32; 25,32</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,98; 28,16</t>
+          <t>21,87; 28,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,88; 22,83</t>
+          <t>16,97; 23,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,66; 20,79</t>
+          <t>14,48; 20,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,49; 22,87</t>
+          <t>18,69; 23,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,3; 25,96</t>
+          <t>20,96; 25,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,76; 21,99</t>
+          <t>17,66; 21,85</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,85; 18,41</t>
+          <t>13,89; 18,48</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,95; 24,6</t>
+          <t>15,68; 25,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,04; 32,54</t>
+          <t>21,25; 33,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,96; 23,42</t>
+          <t>13,96; 23,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,52; 23,96</t>
+          <t>13,45; 24,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,83; 27,43</t>
+          <t>17,65; 28,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,68; 23,39</t>
+          <t>13,78; 23,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,87; 25,33</t>
+          <t>15,29; 25,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,97; 21,91</t>
+          <t>12,26; 22,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,46; 24,6</t>
+          <t>17,57; 24,44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,8; 26,23</t>
+          <t>18,7; 26,15</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,93; 22,89</t>
+          <t>15,76; 22,58</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,95; 21,5</t>
+          <t>14,41; 21,91</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,38; 22,11</t>
+          <t>17,17; 21,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,19; 25,42</t>
+          <t>20,5; 25,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,03; 22,98</t>
+          <t>18,26; 23,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,5; 17,68</t>
+          <t>12,62; 18,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,06; 25,12</t>
+          <t>19,9; 25,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,19; 25,29</t>
+          <t>20,33; 25,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,19; 22,11</t>
+          <t>17,47; 22,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,09; 19,64</t>
+          <t>14,87; 19,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,37; 22,86</t>
+          <t>19,37; 22,66</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,08; 24,55</t>
+          <t>21,09; 24,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,44; 21,8</t>
+          <t>18,33; 21,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,55; 18,14</t>
+          <t>14,46; 18,27</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>19978</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19379</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>19229</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6545</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>20622</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>17351</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>12114</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>9434</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>40600</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>36730</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>31343</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>15979</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>14303; 27274</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13572; 26469</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13671; 25348</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3077; 11415</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>14815; 27453</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>11809; 24719</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7459; 18160</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>5522; 15777</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>32285; 49754</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>28068; 46111</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>23788; 39594</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>10378; 23380</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>79372</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>99983</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>92829</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>66237</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>105969</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>122092</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96669</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>91249</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>185340</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>222076</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>189498</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>157487</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>67554; 92964</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>86705; 115291</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>80285; 108377</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>52550; 81761</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>91636; 121591</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>107609; 139976</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>82503; 112383</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>74791; 108118</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>166910; 205969</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>197777; 241768</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>169105; 209281</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>135641; 180381</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>34237</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>43783</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>31829</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>27531</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>35246</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>31137</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>37335</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>30910</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>69484</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>74920</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>69164</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>58441</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>27286; 44716</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35312; 55158</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>24027; 40454</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>20116; 37009</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>27908; 45164</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>23727; 39988</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>28457; 46546</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>22479; 41675</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>58358; 81201</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>63265; 88496</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>56443; 80894</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>47986; 72950</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>133587</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>163145</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>143886</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>100314</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>161836</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>170581</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>146119</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>131592</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>295424</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>333726</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>290005</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>231906</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>116961; 149439</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>145520; 180809</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>128350; 163278</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>83813; 121108</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>143641; 181542</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>152584; 191075</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>129406; 164987</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>113277; 149728</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>271698; 317884</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>308072; 360647</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>264740; 313988</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>206243; 260478</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP17-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP17-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,74; 30,02</t>
+          <t>15,66; 30,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,69; 28,66</t>
+          <t>15,28; 29,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,02; 42,69</t>
+          <t>23,34; 42,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,63; 20,88</t>
+          <t>6,03; 20,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,06; 31,61</t>
+          <t>16,79; 31,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,7; 28,68</t>
+          <t>14,39; 28,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,87; 26,47</t>
+          <t>10,97; 26,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,91; 25,45</t>
+          <t>8,55; 25,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,17; 28,0</t>
+          <t>18,14; 29,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,72; 25,82</t>
+          <t>16,27; 26,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,59; 30,93</t>
+          <t>18,58; 30,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,89; 20,04</t>
+          <t>9,26; 20,25</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,24; 22,34</t>
+          <t>16,34; 22,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,21; 25,54</t>
+          <t>19,29; 25,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,02; 22,98</t>
+          <t>16,89; 22,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,43; 17,79</t>
+          <t>11,07; 17,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,21; 25,49</t>
+          <t>19,21; 25,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,87; 28,44</t>
+          <t>21,87; 28,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,97; 23,12</t>
+          <t>16,9; 22,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,48; 20,93</t>
+          <t>14,98; 21,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,69; 23,06</t>
+          <t>18,71; 23,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20,96; 25,62</t>
+          <t>21,52; 25,83</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,66; 21,85</t>
+          <t>17,46; 21,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,89; 18,48</t>
+          <t>14,11; 18,52</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,68; 25,69</t>
+          <t>14,99; 24,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,25; 33,2</t>
+          <t>21,0; 32,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,96; 23,51</t>
+          <t>14,19; 24,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,45; 24,75</t>
+          <t>13,89; 24,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,65; 28,56</t>
+          <t>17,03; 27,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,78; 23,22</t>
+          <t>13,52; 23,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,29; 25,01</t>
+          <t>15,46; 25,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,26; 22,73</t>
+          <t>11,85; 22,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,57; 24,44</t>
+          <t>17,44; 24,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,7; 26,15</t>
+          <t>18,59; 26,25</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,76; 22,58</t>
+          <t>16,11; 22,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,41; 21,91</t>
+          <t>14,09; 21,07</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,17; 21,94</t>
+          <t>17,17; 22,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,5; 25,47</t>
+          <t>20,46; 25,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,26; 23,22</t>
+          <t>18,16; 23,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,62; 18,24</t>
+          <t>12,5; 17,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,9; 25,15</t>
+          <t>19,83; 24,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,33; 25,46</t>
+          <t>20,12; 25,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,47; 22,27</t>
+          <t>17,53; 22,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,87; 19,65</t>
+          <t>14,87; 19,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,37; 22,66</t>
+          <t>19,45; 22,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,09; 24,69</t>
+          <t>21,02; 24,81</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,33; 21,75</t>
+          <t>18,47; 21,93</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,46; 18,27</t>
+          <t>14,61; 18,08</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14303; 27274</t>
+          <t>14226; 27286</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13572; 26469</t>
+          <t>14118; 26820</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13671; 25348</t>
+          <t>13858; 25495</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3077; 11415</t>
+          <t>3295; 11394</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14815; 27453</t>
+          <t>14582; 27672</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11809; 24719</t>
+          <t>12406; 24702</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7459; 18160</t>
+          <t>7526; 18192</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5522; 15777</t>
+          <t>5303; 16010</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32285; 49754</t>
+          <t>32235; 51607</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28068; 46111</t>
+          <t>29051; 46537</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23788; 39594</t>
+          <t>23778; 39498</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10378; 23380</t>
+          <t>10807; 23629</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>67554; 92964</t>
+          <t>67989; 92706</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>86705; 115291</t>
+          <t>87103; 116094</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80285; 108377</t>
+          <t>79656; 107140</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52550; 81761</t>
+          <t>50885; 81530</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>91636; 121591</t>
+          <t>91616; 120915</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>107609; 139976</t>
+          <t>107633; 138965</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>82503; 112383</t>
+          <t>82171; 111044</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>74791; 108118</t>
+          <t>77386; 109264</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>166910; 205969</t>
+          <t>167129; 207509</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>197777; 241768</t>
+          <t>203081; 243745</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>169105; 209281</t>
+          <t>167209; 208567</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>135641; 180381</t>
+          <t>137760; 180786</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27286; 44716</t>
+          <t>26097; 42894</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35312; 55158</t>
+          <t>34887; 53408</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24027; 40454</t>
+          <t>24422; 41382</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20116; 37009</t>
+          <t>20774; 35898</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27908; 45164</t>
+          <t>26925; 43850</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23727; 39988</t>
+          <t>23283; 40295</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28457; 46546</t>
+          <t>28767; 47045</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22479; 41675</t>
+          <t>21728; 41250</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>58358; 81201</t>
+          <t>57942; 82024</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63265; 88496</t>
+          <t>62895; 88835</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56443; 80894</t>
+          <t>57698; 81782</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>47986; 72950</t>
+          <t>46915; 70132</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>116961; 149439</t>
+          <t>116903; 151293</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>145520; 180809</t>
+          <t>145285; 183629</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>128350; 163278</t>
+          <t>127645; 161928</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>83813; 121108</t>
+          <t>83018; 116624</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>143641; 181542</t>
+          <t>143154; 180250</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>152584; 191075</t>
+          <t>151019; 189517</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>129406; 164987</t>
+          <t>129843; 164378</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>113277; 149728</t>
+          <t>113296; 151520</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>271698; 317884</t>
+          <t>272887; 321100</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>308072; 360647</t>
+          <t>306933; 362347</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>264740; 313988</t>
+          <t>266751; 316631</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>206243; 260478</t>
+          <t>208300; 257858</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP17-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP17-Estudios-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
+          <t>Menores que han necesitado consulta médica en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>23,75%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20,13%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17,66%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16,02%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>21,99%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>20,98%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>32,38%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11,97%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>23,75%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20,13%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,66%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,66; 30,03</t>
+          <t>16,79; 31,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,28; 29,04</t>
+          <t>14,02; 28,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,34; 42,94</t>
+          <t>11,38; 27,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,03; 20,84</t>
+          <t>9,61; 26,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,79; 31,86</t>
+          <t>15,56; 29,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,39; 28,66</t>
+          <t>14,66; 28,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,97; 26,51</t>
+          <t>23,69; 43,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,55; 25,82</t>
+          <t>7,09; 22,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,14; 29,04</t>
+          <t>17,99; 28,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,27; 26,06</t>
+          <t>15,9; 26,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,58; 30,86</t>
+          <t>18,43; 30,98</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,26; 20,25</t>
+          <t>10,14; 21,18</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>22,22%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24,81%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>19,89%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17,62%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>19,08%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>22,15%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>19,68%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>14,41%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>22,22%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>24,81%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>19,89%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,34; 22,28</t>
+          <t>19,32; 25,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,29; 25,72</t>
+          <t>21,98; 28,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,89; 22,72</t>
+          <t>16,88; 22,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,07; 17,74</t>
+          <t>14,52; 20,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,21; 25,35</t>
+          <t>15,92; 22,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,87; 28,24</t>
+          <t>19,21; 25,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,9; 22,84</t>
+          <t>16,89; 22,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,98; 21,15</t>
+          <t>11,63; 17,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,71; 23,24</t>
+          <t>18,49; 22,87</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,52; 25,83</t>
+          <t>21,3; 25,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,46; 21,78</t>
+          <t>17,76; 21,99</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,11; 18,52</t>
+          <t>14,01; 18,41</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>22,29%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18,08%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>20,06%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17,11%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>19,67%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>26,35%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>18,49%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>18,41%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>22,29%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>18,08%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>20,06%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,99; 24,64</t>
+          <t>16,83; 27,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,0; 32,15</t>
+          <t>13,68; 23,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,19; 24,05</t>
+          <t>15,87; 25,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,89; 24,0</t>
+          <t>12,08; 22,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,03; 27,73</t>
+          <t>14,95; 24,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,52; 23,4</t>
+          <t>21,04; 32,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,46; 25,28</t>
+          <t>13,96; 23,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,85; 22,5</t>
+          <t>13,02; 23,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,44; 24,69</t>
+          <t>17,46; 24,6</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,59; 26,25</t>
+          <t>18,8; 26,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,11; 22,83</t>
+          <t>15,93; 22,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,09; 21,07</t>
+          <t>13,84; 21,33</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>22,42%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>22,73%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19,72%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17,37%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>19,62%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>22,98%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>20,47%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15,11%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>22,42%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>22,73%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,72%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,17; 22,22</t>
+          <t>20,06; 25,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,46; 25,86</t>
+          <t>20,19; 25,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,16; 23,03</t>
+          <t>17,19; 22,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,5; 17,57</t>
+          <t>15,03; 19,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,83; 24,97</t>
+          <t>17,38; 22,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,12; 25,25</t>
+          <t>20,19; 25,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,53; 22,19</t>
+          <t>18,03; 22,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,87; 19,89</t>
+          <t>12,86; 17,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,45; 22,89</t>
+          <t>19,37; 22,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,02; 24,81</t>
+          <t>21,08; 24,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,47; 21,93</t>
+          <t>18,44; 21,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,61; 18,08</t>
+          <t>14,63; 18,04</t>
         </is>
       </c>
     </row>
@@ -1246,13 +1246,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
+          <t>Menores que han necesitado consulta médica en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>20622</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17351</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12114</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>19978</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>19379</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>19229</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6545</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>20622</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17351</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>12114</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>15045</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14226; 27286</t>
+          <t>14583; 27368</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14118; 26820</t>
+          <t>12080; 24464</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13858; 25495</t>
+          <t>7805; 19010</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3295; 11394</t>
+          <t>5454; 15082</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14582; 27672</t>
+          <t>14138; 26784</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12406; 24702</t>
+          <t>13544; 26322</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7526; 18192</t>
+          <t>14066; 25805</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5303; 16010</t>
+          <t>3316; 10519</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32235; 51607</t>
+          <t>31972; 50661</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29051; 46537</t>
+          <t>28398; 46449</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23778; 39498</t>
+          <t>23589; 39658</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10807; 23629</t>
+          <t>10496; 21924</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>146</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>146</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>98</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>105969</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>122092</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>96669</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>83807</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>79372</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>99983</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>92829</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>66237</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>105969</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>122092</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96669</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>91249</t>
+          <t>63226</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>157487</t>
+          <t>147032</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>67989; 92706</t>
+          <t>92144; 120769</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87103; 116094</t>
+          <t>108189; 138572</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79656; 107140</t>
+          <t>82064; 111001</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50885; 81530</t>
+          <t>69047; 99850</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>91616; 120915</t>
+          <t>66230; 91866</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>107633; 138965</t>
+          <t>86724; 115062</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>82171; 111044</t>
+          <t>79663; 106072</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>77386; 109264</t>
+          <t>50179; 75294</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>167129; 207509</t>
+          <t>165174; 204278</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>203081; 243745</t>
+          <t>200941; 244941</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>167209; 208567</t>
+          <t>170128; 210595</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>137760; 180786</t>
+          <t>127146; 167023</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>44</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>35246</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>31137</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>37335</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>28824</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>34237</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>43783</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>31829</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>27531</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>35246</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>31137</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>37335</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30910</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>58441</t>
+          <t>55155</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26097; 42894</t>
+          <t>26622; 43376</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34887; 53408</t>
+          <t>23557; 40283</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24422; 41382</t>
+          <t>29543; 47145</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20774; 35898</t>
+          <t>20343; 37720</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>26925; 43850</t>
+          <t>26030; 42821</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23283; 40295</t>
+          <t>34958; 54055</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28767; 47045</t>
+          <t>24016; 40302</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21728; 41250</t>
+          <t>19527; 34596</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>57942; 82024</t>
+          <t>57997; 81722</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62895; 88835</t>
+          <t>63618; 88738</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>57698; 81782</t>
+          <t>57064; 82014</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>46915; 70132</t>
+          <t>44055; 67928</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>235</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>223</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>153</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>161836</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>170581</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>146119</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>133587</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>163145</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>143886</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>161836</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>170581</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>146119</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217233</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>116903; 151293</t>
+          <t>144815; 181338</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>145285; 183629</t>
+          <t>151568; 189843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>127645; 161928</t>
+          <t>127328; 163833</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>83018; 116624</t>
+          <t>105312; 138293</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>143154; 180250</t>
+          <t>118374; 150599</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>151019; 189517</t>
+          <t>143342; 180478</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>129843; 164378</t>
+          <t>126750; 161597</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>113296; 151520</t>
+          <t>80789; 110508</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>272887; 321100</t>
+          <t>271796; 320791</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>306933; 362347</t>
+          <t>307930; 358551</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>266751; 316631</t>
+          <t>266309; 314781</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>208300; 257858</t>
+          <t>194488; 239724</t>
         </is>
       </c>
     </row>
